--- a/results/Int Task Remove ACC -0.3/Rando_7_permute.xlsx
+++ b/results/Int Task Remove ACC -0.3/Rando_7_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7030342921322092</v>
+        <v>0.7133625300232407</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6982007934887249</v>
+        <v>0.7402211752579324</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6948028190242812</v>
+        <v>0.7112748816087595</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6948028190242812</v>
+        <v>0.7114954977294164</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7168729397006914</v>
+        <v>0.7114954977294164</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7001468343106081</v>
+        <v>0.6924726752044498</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6900209798029893</v>
+        <v>0.6882359948267647</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6766472670342386</v>
+        <v>0.6901340227739043</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6784577778426053</v>
+        <v>0.6901340227739043</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6811720246603848</v>
+        <v>0.6871329142234799</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6715937600280055</v>
+        <v>0.7077225366356468</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6678639497457142</v>
+        <v>0.6665232358003442</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6621923529468965</v>
+        <v>0.6665232358003442</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6574925610432043</v>
+        <v>0.6424499450586851</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6604736135826599</v>
+        <v>0.6361158921399885</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6761896253294047</v>
+        <v>0.642957422911987</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6869159446502717</v>
+        <v>0.6487390238921789</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6814205976448166</v>
+        <v>0.6710072736466447</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6811337359121716</v>
+        <v>0.6710072736466447</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6752840660462673</v>
+        <v>0.6628414383927964</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6752840660462673</v>
+        <v>0.6723960004667581</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6729466291315382</v>
+        <v>0.6530218938708831</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6752415229926971</v>
+        <v>0.6531543850948589</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6665019642735591</v>
+        <v>0.6361639050147321</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6681137382459621</v>
+        <v>0.629852946896545</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6729241420889368</v>
+        <v>0.6239388546923773</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.672637280356292</v>
+        <v>0.6249319311142877</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6878877495453971</v>
+        <v>0.6162160749535673</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6842685512023883</v>
+        <v>0.6269186917160167</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6716241479234127</v>
+        <v>0.604563532580686</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6581422542470122</v>
+        <v>0.6067478145025623</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6601721656602195</v>
+        <v>0.6064609527699174</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6676080836663847</v>
+        <v>0.6047166875735387</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6486089636998357</v>
+        <v>0.5770017114462693</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6513894561296032</v>
+        <v>0.5852113052695042</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6076764685862093</v>
+        <v>0.5863362651574823</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5941690490776665</v>
+        <v>0.5847244911850793</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6159517002635239</v>
+        <v>0.5492223129807365</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6051396870776082</v>
+        <v>0.5477649095170026</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.594745811332497</v>
+        <v>0.5489129642054902</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6176528146484241</v>
+        <v>0.5836669924249054</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6290604305843228</v>
+        <v>0.5898649075721774</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6290604305843228</v>
+        <v>0.603547361358266</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6467346383111137</v>
+        <v>0.6044723688944641</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6472858747338021</v>
+        <v>0.5732956037223956</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6406880548829701</v>
+        <v>0.5773997928761049</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6406880548829701</v>
+        <v>0.5579564018787012</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6540374573353949</v>
+        <v>0.5711301622956718</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6445716279160224</v>
+        <v>0.5602689207191964</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6159085494520454</v>
+        <v>0.5432310355222343</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6167691346499801</v>
+        <v>0.4890105215049058</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6163497816933594</v>
+        <v>0.496975796649066</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6308685103610568</v>
+        <v>0.477581026284314</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.618976511372366</v>
+        <v>0.4369755049252701</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6166816175112071</v>
+        <v>0.4681151968649416</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6397630473467721</v>
+        <v>0.4949337300776958</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6436022540525297</v>
+        <v>0.4959268064996062</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6298772572128708</v>
+        <v>0.4947793595690267</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6277373416182892</v>
+        <v>0.4747203098106713</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6207645351381312</v>
+        <v>0.4795750799809407</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6204114277934984</v>
+        <v>0.4875026741347959</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6186227962698251</v>
+        <v>0.4915843762459037</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6204715958264049</v>
+        <v>0.4991995828349718</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5843938708830478</v>
+        <v>0.4914318290109591</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5814371286599181</v>
+        <v>0.4923799313476667</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5948096259128524</v>
+        <v>0.4737983410640139</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6121343728424594</v>
+        <v>0.4704915302857921</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6271380923208573</v>
+        <v>0.4761400322841001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6337577914563824</v>
+        <v>0.4761400322841001</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6301167138286803</v>
+        <v>0.4782149177825102</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6632127784746735</v>
+        <v>0.4737351342415667</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7219726363079436</v>
+        <v>0.4903968172933866</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6696349562900512</v>
+        <v>0.4817903575561325</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6445691968843899</v>
+        <v>0.4823640810214223</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6461815786147009</v>
+        <v>0.4882350224141117</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5976047045324153</v>
+        <v>0.4882350224141117</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5976047045324153</v>
+        <v>0.4905293085173624</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5757740404718146</v>
+        <v>0.4674442321343485</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5543232251038051</v>
+        <v>0.4674442321343485</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5559915205616656</v>
+        <v>0.4670248791777279</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.565569785194045</v>
+        <v>0.4668705086690588</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5505368933360562</v>
+        <v>0.4668705086690588</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5590983789881074</v>
+        <v>0.4813260305143091</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5236721705222829</v>
+        <v>0.4850777200812937</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5339724515495397</v>
+        <v>0.493351736242792</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5042439734725828</v>
+        <v>0.4929554780866808</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.501595364508883</v>
+        <v>0.4905056059589448</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5050905802386301</v>
+        <v>0.5117497836381847</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5015212180440892</v>
+        <v>0.5086392786642939</v>
       </c>
     </row>
   </sheetData>
